--- a/Daily_Report/Top 7 broker List with its Turnover 2024-06-25.xlsx
+++ b/Daily_Report/Top 7 broker List with its Turnover 2024-06-25.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="277">
   <si>
     <t>Date: 2024-06-25</t>
   </si>
@@ -59,12 +59,12 @@
     <t>7</t>
   </si>
   <si>
+    <t>Naasa Securities Co. Ltd.</t>
+  </si>
+  <si>
     <t>Sani Securities Company Limited</t>
   </si>
   <si>
-    <t>Naasa Securities Co. Ltd.</t>
-  </si>
-  <si>
     <t>Imperial Securities Co .Pvt.Limited</t>
   </si>
   <si>
@@ -80,12 +80,12 @@
     <t>Dipshika Dhitopatra Karobar Co. Pvt.Limited</t>
   </si>
   <si>
+    <t>58</t>
+  </si>
+  <si>
     <t>42</t>
   </si>
   <si>
-    <t>58</t>
-  </si>
-  <si>
     <t>45</t>
   </si>
   <si>
@@ -101,67 +101,67 @@
     <t>38</t>
   </si>
   <si>
-    <t>554,678,232.0</t>
-  </si>
-  <si>
-    <t>450,913,145.5</t>
-  </si>
-  <si>
-    <t>361,057,371.64</t>
-  </si>
-  <si>
-    <t>352,885,065.1</t>
-  </si>
-  <si>
-    <t>258,796,225.4</t>
-  </si>
-  <si>
-    <t>231,630,973.9</t>
-  </si>
-  <si>
-    <t>212,976,026.0</t>
-  </si>
-  <si>
-    <t>227,892,593.6</t>
-  </si>
-  <si>
-    <t>243,406,712.0</t>
-  </si>
-  <si>
-    <t>191,857,041.4</t>
-  </si>
-  <si>
-    <t>179,109,905.4</t>
-  </si>
-  <si>
-    <t>130,133,577.9</t>
-  </si>
-  <si>
-    <t>111,208,355.0</t>
-  </si>
-  <si>
-    <t>109,361,277.9</t>
-  </si>
-  <si>
-    <t>326,785,638.39</t>
-  </si>
-  <si>
-    <t>207,506,433.5</t>
-  </si>
-  <si>
-    <t>169,200,330.24</t>
-  </si>
-  <si>
-    <t>173,775,159.7</t>
-  </si>
-  <si>
-    <t>128,662,647.5</t>
-  </si>
-  <si>
-    <t>120,422,618.9</t>
-  </si>
-  <si>
-    <t>103,614,748.1</t>
+    <t>439,374,192.7</t>
+  </si>
+  <si>
+    <t>434,011,434.7</t>
+  </si>
+  <si>
+    <t>354,675,712.04</t>
+  </si>
+  <si>
+    <t>350,701,551.4</t>
+  </si>
+  <si>
+    <t>258,877,557.2</t>
+  </si>
+  <si>
+    <t>230,810,968.2</t>
+  </si>
+  <si>
+    <t>212,345,773.2</t>
+  </si>
+  <si>
+    <t>230,408,578.5</t>
+  </si>
+  <si>
+    <t>184,773,289.3</t>
+  </si>
+  <si>
+    <t>184,735,072.4</t>
+  </si>
+  <si>
+    <t>177,255,936.5</t>
+  </si>
+  <si>
+    <t>130,449,999.7</t>
+  </si>
+  <si>
+    <t>110,524,146.0</t>
+  </si>
+  <si>
+    <t>109,588,837.9</t>
+  </si>
+  <si>
+    <t>208,965,614.2</t>
+  </si>
+  <si>
+    <t>249,238,145.4</t>
+  </si>
+  <si>
+    <t>169,940,639.63</t>
+  </si>
+  <si>
+    <t>173,445,614.9</t>
+  </si>
+  <si>
+    <t>128,427,557.5</t>
+  </si>
+  <si>
+    <t>120,286,822.2</t>
+  </si>
+  <si>
+    <t>102,756,935.3</t>
   </si>
   <si>
     <t>Top 5 Buy</t>
@@ -179,10 +179,37 @@
     <t>% of turnover</t>
   </si>
   <si>
+    <t>NRN</t>
+  </si>
+  <si>
+    <t>22,769,312.6</t>
+  </si>
+  <si>
     <t>RSDC</t>
   </si>
   <si>
-    <t>86,445,167.0</t>
+    <t>17,503,564.5</t>
+  </si>
+  <si>
+    <t>LSL</t>
+  </si>
+  <si>
+    <t>8,270,845.2</t>
+  </si>
+  <si>
+    <t>GILB</t>
+  </si>
+  <si>
+    <t>7,713,620.5</t>
+  </si>
+  <si>
+    <t>HURJA</t>
+  </si>
+  <si>
+    <t>6,294,214.5</t>
+  </si>
+  <si>
+    <t>44,814,141.0</t>
   </si>
   <si>
     <t>GVL</t>
@@ -194,7 +221,7 @@
     <t>SHPC</t>
   </si>
   <si>
-    <t>10,850,089.7</t>
+    <t>10,529,189.69</t>
   </si>
   <si>
     <t>HPPL</t>
@@ -209,34 +236,7 @@
     <t>4,581,570.0</t>
   </si>
   <si>
-    <t>30,352,564.5</t>
-  </si>
-  <si>
-    <t>NRN</t>
-  </si>
-  <si>
-    <t>22,769,312.6</t>
-  </si>
-  <si>
-    <t>LSL</t>
-  </si>
-  <si>
-    <t>8,270,845.2</t>
-  </si>
-  <si>
-    <t>GILB</t>
-  </si>
-  <si>
-    <t>7,713,620.5</t>
-  </si>
-  <si>
-    <t>HURJA</t>
-  </si>
-  <si>
-    <t>6,172,214.5</t>
-  </si>
-  <si>
-    <t>22,111,893.7</t>
+    <t>15,657,002.7</t>
   </si>
   <si>
     <t>ACLBSL</t>
@@ -251,40 +251,40 @@
     <t>3,938,884.0</t>
   </si>
   <si>
+    <t>MFIL</t>
+  </si>
+  <si>
+    <t>3,724,187.0</t>
+  </si>
+  <si>
     <t>PFL</t>
   </si>
   <si>
     <t>3,708,169.1</t>
   </si>
   <si>
-    <t>SIFC</t>
-  </si>
-  <si>
-    <t>3,577,432.5</t>
-  </si>
-  <si>
     <t>NFS</t>
   </si>
   <si>
     <t>15,235,435.6</t>
   </si>
   <si>
-    <t>10,452,187.6</t>
-  </si>
-  <si>
     <t>CKHL</t>
   </si>
   <si>
     <t>9,730,403.9</t>
   </si>
   <si>
+    <t>8,524,337.6</t>
+  </si>
+  <si>
     <t>SCB</t>
   </si>
   <si>
     <t>5,769,896.0</t>
   </si>
   <si>
-    <t>4,156,548.5</t>
+    <t>4,190,048.5</t>
   </si>
   <si>
     <t>10,619,140.19</t>
@@ -299,13 +299,10 @@
     <t>SFCL</t>
   </si>
   <si>
-    <t>3,513,570.6</t>
-  </si>
-  <si>
-    <t>MFIL</t>
-  </si>
-  <si>
-    <t>3,467,399.0</t>
+    <t>3,527,430.6</t>
+  </si>
+  <si>
+    <t>3,428,549.0</t>
   </si>
   <si>
     <t>ICFC</t>
@@ -320,7 +317,7 @@
     <t>4,892,210.0</t>
   </si>
   <si>
-    <t>3,891,745.7</t>
+    <t>3,853,465.7</t>
   </si>
   <si>
     <t>3,813,592.0</t>
@@ -329,7 +326,7 @@
     <t>RLFL</t>
   </si>
   <si>
-    <t>3,622,731.7</t>
+    <t>3,600,481.7</t>
   </si>
   <si>
     <t>USHEC</t>
@@ -359,13 +356,31 @@
     <t>3,429,731.9</t>
   </si>
   <si>
-    <t>3,119,620.1</t>
+    <t>3,173,076.1</t>
   </si>
   <si>
     <t>Sell Amount</t>
   </si>
   <si>
-    <t>182,717,822.8</t>
+    <t>20,209,192.1</t>
+  </si>
+  <si>
+    <t>SSHL</t>
+  </si>
+  <si>
+    <t>15,716,462.8</t>
+  </si>
+  <si>
+    <t>12,947,789.0</t>
+  </si>
+  <si>
+    <t>12,340,893.0</t>
+  </si>
+  <si>
+    <t>5,139,393.4</t>
+  </si>
+  <si>
+    <t>105,681,533.8</t>
   </si>
   <si>
     <t>29,554,120.3</t>
@@ -377,7 +392,7 @@
     <t>GUFL</t>
   </si>
   <si>
-    <t>6,004,324.4</t>
+    <t>5,698,314.4</t>
   </si>
   <si>
     <t>MSLB</t>
@@ -386,24 +401,6 @@
     <t>3,589,783.9</t>
   </si>
   <si>
-    <t>20,258,678.1</t>
-  </si>
-  <si>
-    <t>SSHL</t>
-  </si>
-  <si>
-    <t>15,496,342.8</t>
-  </si>
-  <si>
-    <t>12,644,338.0</t>
-  </si>
-  <si>
-    <t>11,784,779.0</t>
-  </si>
-  <si>
-    <t>5,139,393.4</t>
-  </si>
-  <si>
     <t>NTC</t>
   </si>
   <si>
@@ -413,7 +410,7 @@
     <t>5,855,830.9</t>
   </si>
   <si>
-    <t>4,982,542.09</t>
+    <t>5,635,742.1</t>
   </si>
   <si>
     <t>4,413,881.7</t>
@@ -431,7 +428,7 @@
     <t>PROFL</t>
   </si>
   <si>
-    <t>5,260,914.4</t>
+    <t>5,252,614.4</t>
   </si>
   <si>
     <t>4,625,046.0</t>
@@ -443,7 +440,7 @@
     <t>SADBL</t>
   </si>
   <si>
-    <t>4,048,318.5</t>
+    <t>3,806,973.5</t>
   </si>
   <si>
     <t>GRDBL</t>
@@ -452,7 +449,7 @@
     <t>6,123,653.9</t>
   </si>
   <si>
-    <t>5,329,078.0</t>
+    <t>5,508,126.0</t>
   </si>
   <si>
     <t>5,081,284.9</t>
@@ -491,7 +488,7 @@
     <t>4,115,459.5</t>
   </si>
   <si>
-    <t>3,013,280.0</t>
+    <t>3,059,155.2</t>
   </si>
   <si>
     <t>NGPL</t>
@@ -500,7 +497,7 @@
     <t>2,911,442.1</t>
   </si>
   <si>
-    <t>2,687,778.5</t>
+    <t>2,653,678.5</t>
   </si>
   <si>
     <t>SARBTM</t>
@@ -524,88 +521,88 @@
     <t>Percentage (%)</t>
   </si>
   <si>
-    <t>225,344,305.6</t>
-  </si>
-  <si>
-    <t>125,912,750.7</t>
-  </si>
-  <si>
-    <t>94,684,099.4</t>
-  </si>
-  <si>
-    <t>92,712,067.0</t>
+    <t>148,308,016.6</t>
+  </si>
+  <si>
+    <t>126,231,466.7</t>
+  </si>
+  <si>
+    <t>96,964,205.2</t>
+  </si>
+  <si>
+    <t>94,919,480.4</t>
   </si>
   <si>
     <t>HATHY</t>
   </si>
   <si>
-    <t>91,042,536.2</t>
+    <t>85,493,489.7</t>
   </si>
   <si>
     <t>Hydro Power</t>
   </si>
   <si>
-    <t>955,229,626.5</t>
+    <t>950,509,666.0</t>
   </si>
   <si>
     <t>Promoter Shares/debenture</t>
   </si>
   <si>
-    <t>927,614,427.8</t>
+    <t>914,604,611.0</t>
   </si>
   <si>
     <t>Finance</t>
   </si>
   <si>
-    <t>785,143,336.4</t>
+    <t>788,324,256.0</t>
   </si>
   <si>
     <t>Microfinance</t>
   </si>
   <si>
-    <t>701,413,447.0</t>
+    <t>631,343,713.2</t>
   </si>
   <si>
     <t>Development Banks</t>
   </si>
   <si>
-    <t>261,288,119.6</t>
+    <t>257,220,627.7</t>
   </si>
   <si>
     <t>Investment</t>
   </si>
   <si>
-    <t>224,894,925.8</t>
+    <t>225,139,314.1</t>
   </si>
   <si>
     <t>Commercial Banks</t>
   </si>
   <si>
-    <t>138,495,876.69</t>
+    <t>137,636,554.19</t>
   </si>
   <si>
     <t>Manufacturing And Processing</t>
   </si>
   <si>
-    <t>103,454,563.7</t>
+    <t>103,438,443.7</t>
   </si>
   <si>
     <t>Non Life Insurance</t>
   </si>
   <si>
-    <t>54,481,322.0</t>
+    <t>54,222,812.0</t>
   </si>
   <si>
     <t>Life Insurance</t>
   </si>
   <si>
-    <t>47,171,315.7</t>
+    <t>47,119,959.1</t>
   </si>
   <si>
     <t>Hotels And Tourism</t>
   </si>
   <si>
-    <t>33,043,025.5</t>
+    <t>32,960,356.5</t>
   </si>
   <si>
     <t>Others</t>
@@ -623,7 +620,7 @@
     <t>Mutual Fund</t>
   </si>
   <si>
-    <t>4,603,893.59</t>
+    <t>4,435,934.99</t>
   </si>
   <si>
     <t>Tradings</t>
@@ -641,214 +638,214 @@
     <t>100%</t>
   </si>
   <si>
-    <t>97,460,221.1</t>
-  </si>
-  <si>
-    <t>54,379,126.1</t>
-  </si>
-  <si>
-    <t>29,971,479.3</t>
-  </si>
-  <si>
-    <t>17,096,496.5</t>
+    <t>49,077,981.9</t>
+  </si>
+  <si>
+    <t>47,597,839.8</t>
+  </si>
+  <si>
+    <t>41,711,595.1</t>
+  </si>
+  <si>
+    <t>40,016,431.29</t>
+  </si>
+  <si>
+    <t>21,991,617.9</t>
+  </si>
+  <si>
+    <t>55,937,409.1</t>
+  </si>
+  <si>
+    <t>53,068,487.1</t>
+  </si>
+  <si>
+    <t>29,871,348.3</t>
+  </si>
+  <si>
+    <t>17,021,835.7</t>
   </si>
   <si>
     <t>12,233,292.4</t>
   </si>
   <si>
-    <t>62,032,462.9</t>
-  </si>
-  <si>
-    <t>47,638,198.8</t>
-  </si>
-  <si>
-    <t>41,288,388.79</t>
-  </si>
-  <si>
-    <t>40,189,416.1</t>
-  </si>
-  <si>
-    <t>21,996,582.9</t>
-  </si>
-  <si>
-    <t>42,817,954.1</t>
-  </si>
-  <si>
-    <t>42,082,089.5</t>
-  </si>
-  <si>
-    <t>38,098,211.5</t>
-  </si>
-  <si>
-    <t>36,422,760.4</t>
-  </si>
-  <si>
-    <t>11,443,297.2</t>
-  </si>
-  <si>
-    <t>43,268,095.0</t>
-  </si>
-  <si>
-    <t>39,034,828.29</t>
-  </si>
-  <si>
-    <t>32,042,707.6</t>
-  </si>
-  <si>
-    <t>28,718,636.2</t>
+    <t>42,293,021.1</t>
+  </si>
+  <si>
+    <t>38,058,117.5</t>
+  </si>
+  <si>
+    <t>36,241,515.4</t>
+  </si>
+  <si>
+    <t>35,654,588.5</t>
+  </si>
+  <si>
+    <t>11,519,112.2</t>
+  </si>
+  <si>
+    <t>43,266,796.1</t>
+  </si>
+  <si>
+    <t>39,214,474.29</t>
+  </si>
+  <si>
+    <t>32,034,611.6</t>
+  </si>
+  <si>
+    <t>26,684,816.2</t>
   </si>
   <si>
     <t>13,191,467.7</t>
   </si>
   <si>
-    <t>30,582,002.7</t>
-  </si>
-  <si>
-    <t>26,679,838.5</t>
-  </si>
-  <si>
-    <t>24,470,302.1</t>
-  </si>
-  <si>
-    <t>21,694,160.3</t>
-  </si>
-  <si>
-    <t>7,022,422.4</t>
-  </si>
-  <si>
-    <t>27,253,617.8</t>
-  </si>
-  <si>
-    <t>25,325,917.7</t>
-  </si>
-  <si>
-    <t>20,220,398.2</t>
-  </si>
-  <si>
-    <t>13,348,482.6</t>
-  </si>
-  <si>
-    <t>7,088,543.1</t>
-  </si>
-  <si>
-    <t>34,360,111.0</t>
-  </si>
-  <si>
-    <t>24,759,500.7</t>
-  </si>
-  <si>
-    <t>22,823,641.6</t>
-  </si>
-  <si>
-    <t>12,695,547.2</t>
+    <t>30,605,712.7</t>
+  </si>
+  <si>
+    <t>26,449,543.3</t>
+  </si>
+  <si>
+    <t>24,831,382.1</t>
+  </si>
+  <si>
+    <t>21,644,887.3</t>
+  </si>
+  <si>
+    <t>7,233,622.4</t>
+  </si>
+  <si>
+    <t>27,266,559.8</t>
+  </si>
+  <si>
+    <t>25,334,821.7</t>
+  </si>
+  <si>
+    <t>19,590,053.2</t>
+  </si>
+  <si>
+    <t>13,267,712.6</t>
+  </si>
+  <si>
+    <t>7,093,603.1</t>
+  </si>
+  <si>
+    <t>34,292,868.0</t>
+  </si>
+  <si>
+    <t>24,742,317.7</t>
+  </si>
+  <si>
+    <t>22,872,556.6</t>
+  </si>
+  <si>
+    <t>12,960,169.2</t>
   </si>
   <si>
     <t>4,893,400.09</t>
   </si>
   <si>
-    <t>194,944,414.7</t>
-  </si>
-  <si>
-    <t>64,636,534.6</t>
-  </si>
-  <si>
-    <t>25,366,096.0</t>
-  </si>
-  <si>
-    <t>19,560,255.3</t>
-  </si>
-  <si>
-    <t>10,109,637.8</t>
-  </si>
-  <si>
-    <t>66,250,433.4</t>
-  </si>
-  <si>
-    <t>39,811,844.4</t>
-  </si>
-  <si>
-    <t>30,330,061.3</t>
-  </si>
-  <si>
-    <t>29,413,759.8</t>
-  </si>
-  <si>
-    <t>17,596,582.1</t>
-  </si>
-  <si>
-    <t>41,555,789.9</t>
-  </si>
-  <si>
-    <t>38,296,809.1</t>
-  </si>
-  <si>
-    <t>27,568,782.2</t>
-  </si>
-  <si>
-    <t>17,748,533.6</t>
+    <t>66,352,460.4</t>
+  </si>
+  <si>
+    <t>39,891,571.1</t>
+  </si>
+  <si>
+    <t>30,738,543.3</t>
+  </si>
+  <si>
+    <t>29,955,863.8</t>
+  </si>
+  <si>
+    <t>17,900,033.1</t>
+  </si>
+  <si>
+    <t>117,892,714.7</t>
+  </si>
+  <si>
+    <t>64,601,732.6</t>
+  </si>
+  <si>
+    <t>25,323,017.0</t>
+  </si>
+  <si>
+    <t>19,220,095.3</t>
+  </si>
+  <si>
+    <t>10,054,825.8</t>
+  </si>
+  <si>
+    <t>42,437,022.9</t>
+  </si>
+  <si>
+    <t>38,275,830.9</t>
+  </si>
+  <si>
+    <t>27,337,218.2</t>
+  </si>
+  <si>
+    <t>18,051,898.0</t>
   </si>
   <si>
     <t>10,499,403.19</t>
   </si>
   <si>
-    <t>50,796,188.2</t>
-  </si>
-  <si>
-    <t>39,349,762.4</t>
-  </si>
-  <si>
-    <t>26,135,215.8</t>
-  </si>
-  <si>
-    <t>14,399,262.1</t>
-  </si>
-  <si>
-    <t>13,037,520.7</t>
-  </si>
-  <si>
-    <t>37,216,943.4</t>
-  </si>
-  <si>
-    <t>25,448,869.3</t>
-  </si>
-  <si>
-    <t>22,647,098.3</t>
+    <t>50,814,968.2</t>
+  </si>
+  <si>
+    <t>39,381,170.6</t>
+  </si>
+  <si>
+    <t>26,079,303.8</t>
+  </si>
+  <si>
+    <t>14,380,655.1</t>
+  </si>
+  <si>
+    <t>12,796,175.7</t>
+  </si>
+  <si>
+    <t>36,990,393.4</t>
+  </si>
+  <si>
+    <t>25,326,292.3</t>
+  </si>
+  <si>
+    <t>22,863,911.3</t>
   </si>
   <si>
     <t>13,652,425.8</t>
   </si>
   <si>
-    <t>13,099,321.3</t>
-  </si>
-  <si>
-    <t>33,071,996.3</t>
-  </si>
-  <si>
-    <t>29,125,987.2</t>
-  </si>
-  <si>
-    <t>25,923,448.3</t>
-  </si>
-  <si>
-    <t>14,066,640.3</t>
-  </si>
-  <si>
-    <t>5,268,265.9</t>
-  </si>
-  <si>
-    <t>28,490,166.5</t>
-  </si>
-  <si>
-    <t>25,733,415.0</t>
-  </si>
-  <si>
-    <t>22,561,219.8</t>
-  </si>
-  <si>
-    <t>11,342,351.6</t>
-  </si>
-  <si>
-    <t>6,451,237.6</t>
+    <t>12,986,945.3</t>
+  </si>
+  <si>
+    <t>33,140,260.3</t>
+  </si>
+  <si>
+    <t>29,117,738.5</t>
+  </si>
+  <si>
+    <t>25,659,041.3</t>
+  </si>
+  <si>
+    <t>14,077,140.3</t>
+  </si>
+  <si>
+    <t>5,313,865.9</t>
+  </si>
+  <si>
+    <t>27,801,439.5</t>
+  </si>
+  <si>
+    <t>25,716,342.0</t>
+  </si>
+  <si>
+    <t>22,496,495.0</t>
+  </si>
+  <si>
+    <t>11,363,231.6</t>
+  </si>
+  <si>
+    <t>6,343,069.6</t>
   </si>
 </sst>
 </file>
@@ -1657,25 +1654,25 @@
         <v>55</v>
       </c>
       <c r="D9" s="10">
-        <v>0.1558474120902585</v>
+        <v>0.05182214380885735</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F9" s="11" t="s">
         <v>64</v>
       </c>
       <c r="G9" s="12">
-        <v>0.0673135498552459</v>
+        <v>0.1032556688995457</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I9" s="13" t="s">
         <v>73</v>
       </c>
       <c r="J9" s="14">
-        <v>0.06124205025800481</v>
+        <v>0.04414455844733518</v>
       </c>
       <c r="K9" s="15" t="s">
         <v>82</v>
@@ -1684,7 +1681,7 @@
         <v>83</v>
       </c>
       <c r="M9" s="16">
-        <v>0.0431739314206528</v>
+        <v>0.04344273796103886</v>
       </c>
       <c r="N9" s="17" t="s">
         <v>74</v>
@@ -1693,25 +1690,25 @@
         <v>90</v>
       </c>
       <c r="P9" s="18">
-        <v>0.0410328248937436</v>
+        <v>0.04101993357344613</v>
       </c>
       <c r="Q9" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="R9" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="R9" s="15" t="s">
-        <v>100</v>
-      </c>
       <c r="S9" s="16">
-        <v>0.02112070729414655</v>
+        <v>0.02119574315792849</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="V9" s="18">
-        <v>0.01795382030463842</v>
+        <v>0.01800710813489364</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1723,7 +1720,7 @@
         <v>57</v>
       </c>
       <c r="D10" s="10">
-        <v>0.02287166372881927</v>
+        <v>0.03983748884393683</v>
       </c>
       <c r="E10" s="11" t="s">
         <v>65</v>
@@ -1732,7 +1729,7 @@
         <v>66</v>
       </c>
       <c r="G10" s="12">
-        <v>0.05049600533324882</v>
+        <v>0.02923059851814545</v>
       </c>
       <c r="H10" s="13" t="s">
         <v>74</v>
@@ -1741,16 +1738,16 @@
         <v>75</v>
       </c>
       <c r="J10" s="14">
-        <v>0.01381482720417446</v>
+        <v>0.01406339659208879</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>54</v>
+        <v>84</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M10" s="16">
-        <v>0.02961924046583857</v>
+        <v>0.02774553993604033</v>
       </c>
       <c r="N10" s="17" t="s">
         <v>91</v>
@@ -1759,25 +1756,25 @@
         <v>92</v>
       </c>
       <c r="P10" s="18">
-        <v>0.01416737239630544</v>
+        <v>0.01416292141990283</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="S10" s="16">
-        <v>0.01680149089939996</v>
+        <v>0.01669533181222538</v>
       </c>
       <c r="T10" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="U10" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="U10" s="17" t="s">
-        <v>109</v>
-      </c>
       <c r="V10" s="18">
-        <v>0.01777628435981804</v>
+        <v>0.01782904525457256</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1789,7 +1786,7 @@
         <v>59</v>
       </c>
       <c r="D11" s="10">
-        <v>0.01956105192893165</v>
+        <v>0.01882414884036497</v>
       </c>
       <c r="E11" s="11" t="s">
         <v>67</v>
@@ -1798,7 +1795,7 @@
         <v>68</v>
       </c>
       <c r="G11" s="12">
-        <v>0.01834243530609156</v>
+        <v>0.02426016657205829</v>
       </c>
       <c r="H11" s="13" t="s">
         <v>76</v>
@@ -1807,16 +1804,16 @@
         <v>77</v>
       </c>
       <c r="J11" s="14">
-        <v>0.01090930225883146</v>
+        <v>0.01110559270423281</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>85</v>
+        <v>56</v>
       </c>
       <c r="L11" s="15" t="s">
         <v>86</v>
       </c>
       <c r="M11" s="16">
-        <v>0.02757386147028527</v>
+        <v>0.02430652948631353</v>
       </c>
       <c r="N11" s="17" t="s">
         <v>93</v>
@@ -1825,25 +1822,25 @@
         <v>94</v>
       </c>
       <c r="P11" s="18">
-        <v>0.0135765913686313</v>
+        <v>0.01362586482255326</v>
       </c>
       <c r="Q11" s="15" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="R11" s="15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="S11" s="16">
-        <v>0.01646408481469498</v>
+        <v>0.01652257702370316</v>
       </c>
       <c r="T11" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="U11" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="U11" s="17" t="s">
-        <v>111</v>
-      </c>
       <c r="V11" s="18">
-        <v>0.01730814199716545</v>
+        <v>0.01735951342213955</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1855,7 +1852,7 @@
         <v>61</v>
       </c>
       <c r="D12" s="10">
-        <v>0.009727618083271024</v>
+        <v>0.01755592528682443</v>
       </c>
       <c r="E12" s="11" t="s">
         <v>69</v>
@@ -1864,7 +1861,7 @@
         <v>70</v>
       </c>
       <c r="G12" s="12">
-        <v>0.01710666583349808</v>
+        <v>0.01243215631802339</v>
       </c>
       <c r="H12" s="13" t="s">
         <v>78</v>
@@ -1873,7 +1870,7 @@
         <v>79</v>
       </c>
       <c r="J12" s="14">
-        <v>0.01027030436508387</v>
+        <v>0.01050025945836401</v>
       </c>
       <c r="K12" s="15" t="s">
         <v>87</v>
@@ -1882,34 +1879,34 @@
         <v>88</v>
       </c>
       <c r="M12" s="16">
-        <v>0.01635063812736007</v>
+        <v>0.01645243933756947</v>
       </c>
       <c r="N12" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="O12" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="O12" s="17" t="s">
-        <v>96</v>
-      </c>
       <c r="P12" s="18">
-        <v>0.01339818227503406</v>
+        <v>0.01324390200944001</v>
       </c>
       <c r="Q12" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="R12" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="R12" s="15" t="s">
-        <v>104</v>
-      </c>
       <c r="S12" s="16">
-        <v>0.01564010045376751</v>
+        <v>0.01559926604909065</v>
       </c>
       <c r="T12" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="U12" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="U12" s="17" t="s">
-        <v>113</v>
-      </c>
       <c r="V12" s="18">
-        <v>0.01610384025101492</v>
+        <v>0.01615163724860053</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -1921,7 +1918,7 @@
         <v>63</v>
       </c>
       <c r="D13" s="10">
-        <v>0.008259869841079324</v>
+        <v>0.01432540782907935</v>
       </c>
       <c r="E13" s="11" t="s">
         <v>71</v>
@@ -1930,7 +1927,7 @@
         <v>72</v>
       </c>
       <c r="G13" s="12">
-        <v>0.01368825584615829</v>
+        <v>0.01055633477299256</v>
       </c>
       <c r="H13" s="13" t="s">
         <v>80</v>
@@ -1939,43 +1936,43 @@
         <v>81</v>
       </c>
       <c r="J13" s="14">
-        <v>0.009908210664002052</v>
+        <v>0.01045509735829274</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="L13" s="15" t="s">
         <v>89</v>
       </c>
       <c r="M13" s="16">
-        <v>0.01177876003004583</v>
+        <v>0.01194761894629018</v>
       </c>
       <c r="N13" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="O13" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="O13" s="17" t="s">
-        <v>98</v>
-      </c>
       <c r="P13" s="18">
-        <v>0.01309791128043245</v>
+        <v>0.01309379629761123</v>
       </c>
       <c r="Q13" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="R13" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="R13" s="15" t="s">
-        <v>106</v>
-      </c>
       <c r="S13" s="16">
-        <v>0.01517395597325164</v>
+        <v>0.01522786472155183</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="V13" s="18">
-        <v>0.01464775241885676</v>
+        <v>0.01494296802890165</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -1986,7 +1983,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -1995,7 +1992,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>53</v>
@@ -2004,7 +2001,7 @@
         <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>53</v>
@@ -2013,7 +2010,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>53</v>
@@ -2022,7 +2019,7 @@
         <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>53</v>
@@ -2031,7 +2028,7 @@
         <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>53</v>
@@ -2040,7 +2037,7 @@
         <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>53</v>
@@ -2049,519 +2046,519 @@
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D16" s="10">
-        <v>0.3294122831198467</v>
+        <v>0.04599540081271597</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G16" s="12">
-        <v>0.04492811598458932</v>
+        <v>0.2434994227123297</v>
       </c>
       <c r="H16" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="I16" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="I16" s="13" t="s">
-        <v>130</v>
-      </c>
       <c r="J16" s="14">
-        <v>0.02608412025275109</v>
+        <v>0.02655345032179103</v>
       </c>
       <c r="K16" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="L16" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="L16" s="15" t="s">
-        <v>136</v>
-      </c>
       <c r="M16" s="16">
-        <v>0.06520999746327887</v>
+        <v>0.06561600343122977</v>
       </c>
       <c r="N16" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="O16" s="17" t="s">
         <v>143</v>
       </c>
-      <c r="O16" s="17" t="s">
-        <v>144</v>
-      </c>
       <c r="P16" s="18">
-        <v>0.02366206806353212</v>
+        <v>0.0236546341298681</v>
       </c>
       <c r="Q16" s="15" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="R16" s="15" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="S16" s="16">
-        <v>0.03670398762676014</v>
+        <v>0.03683438645183067</v>
       </c>
       <c r="T16" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="U16" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="U16" s="17" t="s">
-        <v>157</v>
-      </c>
       <c r="V16" s="18">
-        <v>0.01932358104944638</v>
+        <v>0.01938093439761484</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C17" s="9" t="s">
         <v>117</v>
       </c>
       <c r="D17" s="10">
-        <v>0.05328155783838296</v>
+        <v>0.03577010908041892</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="G17" s="12">
-        <v>0.03436658024865678</v>
+        <v>0.06809525726074148</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J17" s="14">
-        <v>0.01621856070519087</v>
+        <v>0.01651038033114482</v>
       </c>
       <c r="K17" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="L17" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="L17" s="15" t="s">
-        <v>138</v>
-      </c>
       <c r="M17" s="16">
-        <v>0.0149082942870058</v>
+        <v>0.0149774484288181</v>
       </c>
       <c r="N17" s="17" t="s">
         <v>82</v>
       </c>
       <c r="O17" s="17" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P17" s="18">
-        <v>0.02059179183067018</v>
+        <v>0.0212769544783081</v>
       </c>
       <c r="Q17" s="15" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="R17" s="15" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="S17" s="16">
-        <v>0.01996329731789812</v>
+        <v>0.02003422123333912</v>
       </c>
       <c r="T17" s="17" t="s">
         <v>82</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="V17" s="18">
-        <v>0.01414844692425616</v>
+        <v>0.01440648030756282</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C18" s="9" t="s">
         <v>118</v>
       </c>
       <c r="D18" s="10">
-        <v>0.02192766237850127</v>
+        <v>0.02946870620787828</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="G18" s="12">
-        <v>0.02804162647770933</v>
+        <v>0.02802413952159404</v>
       </c>
       <c r="H18" s="13" t="s">
         <v>82</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J18" s="14">
-        <v>0.0137998625464098</v>
+        <v>0.01588984502937829</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M18" s="16">
-        <v>0.01310638068145321</v>
+        <v>0.01318798272074025</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="O18" s="17" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P18" s="18">
-        <v>0.01963430839126914</v>
+        <v>0.01962813986256202</v>
       </c>
       <c r="Q18" s="15" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="R18" s="15" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="S18" s="16">
-        <v>0.01926334818212324</v>
+        <v>0.01933178537743338</v>
       </c>
       <c r="T18" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="U18" s="17" t="s">
         <v>159</v>
       </c>
-      <c r="U18" s="17" t="s">
-        <v>160</v>
-      </c>
       <c r="V18" s="18">
-        <v>0.01367028089818898</v>
+        <v>0.01371085497076426</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C19" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="C19" s="9" t="s">
-        <v>120</v>
-      </c>
       <c r="D19" s="10">
-        <v>0.01082487837741576</v>
+        <v>0.0280874325461947</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>69</v>
+        <v>124</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G19" s="12">
-        <v>0.02613536357857192</v>
+        <v>0.01312941075835668</v>
       </c>
       <c r="H19" s="13" t="s">
         <v>93</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J19" s="14">
-        <v>0.01222487628476107</v>
+        <v>0.01244483777762095</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="M19" s="16">
-        <v>0.01215070889663446</v>
+        <v>0.01222636079847122</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="O19" s="17" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P19" s="18">
-        <v>0.01889172646333349</v>
+        <v>0.01888579123227295</v>
       </c>
       <c r="Q19" s="15" t="s">
         <v>91</v>
       </c>
       <c r="R19" s="15" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="S19" s="16">
-        <v>0.01904655852245674</v>
+        <v>0.01911422552578678</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U19" s="17" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="V19" s="18">
-        <v>0.01262009884624291</v>
+        <v>0.01249696878826312</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
-        <v>121</v>
+        <v>80</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D20" s="10">
-        <v>0.006471831221961492</v>
+        <v>0.01169707617194787</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>78</v>
+        <v>126</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G20" s="12">
-        <v>0.01139774577718538</v>
+        <v>0.008271173552100884</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J20" s="14">
-        <v>0.01072600036500947</v>
+        <v>0.01091899267002315</v>
       </c>
       <c r="K20" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="L20" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="L20" s="15" t="s">
-        <v>142</v>
-      </c>
       <c r="M20" s="16">
-        <v>0.01147205960346549</v>
+        <v>0.01085530840910902</v>
       </c>
       <c r="N20" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="O20" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="O20" s="17" t="s">
-        <v>149</v>
-      </c>
       <c r="P20" s="18">
-        <v>0.01592974585942319</v>
+        <v>0.01592474119653042</v>
       </c>
       <c r="Q20" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="R20" s="15" t="s">
         <v>154</v>
       </c>
-      <c r="R20" s="15" t="s">
-        <v>155</v>
-      </c>
       <c r="S20" s="16">
-        <v>0.01739568863419608</v>
+        <v>0.01745749056651633</v>
       </c>
       <c r="T20" s="17" t="s">
+        <v>161</v>
+      </c>
+      <c r="U20" s="17" t="s">
         <v>162</v>
       </c>
-      <c r="U20" s="17" t="s">
-        <v>163</v>
-      </c>
       <c r="V20" s="18">
-        <v>0.01243313461018378</v>
+        <v>0.01247003677113927</v>
       </c>
     </row>
     <row r="23" spans="1:22">
       <c r="B23" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="C23" s="19" t="s">
         <v>164</v>
-      </c>
-      <c r="C23" s="19" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="24" spans="1:22">
       <c r="B24" s="20" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="25" spans="1:22">
       <c r="B25" s="20" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="26" spans="1:22">
       <c r="B26" s="20" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="27" spans="1:22">
       <c r="B27" s="20" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="28" spans="1:22">
       <c r="B28" s="20" t="s">
+        <v>172</v>
+      </c>
+      <c r="C28" s="21" t="s">
         <v>173</v>
-      </c>
-      <c r="C28" s="21" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="30" spans="1:22">
       <c r="B30" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="C30" s="19" t="s">
         <v>166</v>
       </c>
-      <c r="C30" s="19" t="s">
+      <c r="D30" s="19" t="s">
         <v>167</v>
-      </c>
-      <c r="D30" s="19" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="31" spans="1:22">
       <c r="B31" s="20" t="s">
+        <v>174</v>
+      </c>
+      <c r="C31" s="21" t="s">
         <v>175</v>
       </c>
-      <c r="C31" s="21" t="s">
-        <v>176</v>
-      </c>
       <c r="D31" s="22">
-        <v>0.228098368757946</v>
+        <v>0.226971293905173</v>
       </c>
     </row>
     <row r="32" spans="1:22">
       <c r="B32" s="20" t="s">
+        <v>176</v>
+      </c>
+      <c r="C32" s="21" t="s">
         <v>177</v>
       </c>
-      <c r="C32" s="21" t="s">
-        <v>178</v>
-      </c>
       <c r="D32" s="22">
-        <v>0.2215041618765323</v>
+        <v>0.2183975601677968</v>
       </c>
     </row>
     <row r="33" spans="2:4">
       <c r="B33" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="C33" s="21" t="s">
         <v>179</v>
       </c>
-      <c r="C33" s="21" t="s">
-        <v>180</v>
-      </c>
       <c r="D33" s="22">
-        <v>0.1874836262461875</v>
+        <v>0.188243194994666</v>
       </c>
     </row>
     <row r="34" spans="2:4">
       <c r="B34" s="20" t="s">
+        <v>180</v>
+      </c>
+      <c r="C34" s="21" t="s">
         <v>181</v>
       </c>
-      <c r="C34" s="21" t="s">
-        <v>182</v>
-      </c>
       <c r="D34" s="22">
-        <v>0.167489846050737</v>
+        <v>0.1507579613439727</v>
       </c>
     </row>
     <row r="35" spans="2:4">
       <c r="B35" s="20" t="s">
+        <v>182</v>
+      </c>
+      <c r="C35" s="21" t="s">
         <v>183</v>
       </c>
-      <c r="C35" s="21" t="s">
-        <v>184</v>
-      </c>
       <c r="D35" s="22">
-        <v>0.06239274013617615</v>
+        <v>0.06142146763625839</v>
       </c>
     </row>
     <row r="36" spans="2:4">
       <c r="B36" s="20" t="s">
+        <v>184</v>
+      </c>
+      <c r="C36" s="21" t="s">
         <v>185</v>
       </c>
-      <c r="C36" s="21" t="s">
-        <v>186</v>
-      </c>
       <c r="D36" s="22">
-        <v>0.05370244420169197</v>
+        <v>0.05376080145007189</v>
       </c>
     </row>
     <row r="37" spans="2:4">
       <c r="B37" s="20" t="s">
+        <v>186</v>
+      </c>
+      <c r="C37" s="21" t="s">
         <v>187</v>
       </c>
-      <c r="C37" s="21" t="s">
-        <v>188</v>
-      </c>
       <c r="D37" s="22">
-        <v>0.0330712979147445</v>
+        <v>0.03286610111698061</v>
       </c>
     </row>
     <row r="38" spans="2:4">
       <c r="B38" s="20" t="s">
+        <v>188</v>
+      </c>
+      <c r="C38" s="21" t="s">
         <v>189</v>
       </c>
-      <c r="C38" s="21" t="s">
-        <v>190</v>
-      </c>
       <c r="D38" s="22">
-        <v>0.02470381630330958</v>
+        <v>0.02469996702392965</v>
       </c>
     </row>
     <row r="39" spans="2:4">
       <c r="B39" s="20" t="s">
+        <v>190</v>
+      </c>
+      <c r="C39" s="21" t="s">
         <v>191</v>
       </c>
-      <c r="C39" s="21" t="s">
-        <v>192</v>
-      </c>
       <c r="D39" s="22">
-        <v>0.01300954276461231</v>
+        <v>0.01294781340899793</v>
       </c>
     </row>
     <row r="40" spans="2:4">
       <c r="B40" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="C40" s="21" t="s">
         <v>193</v>
       </c>
-      <c r="C40" s="21" t="s">
-        <v>194</v>
-      </c>
       <c r="D40" s="22">
-        <v>0.01126399335284445</v>
+        <v>0.01125172995945717</v>
       </c>
     </row>
     <row r="41" spans="2:4">
       <c r="B41" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="C41" s="21" t="s">
         <v>195</v>
       </c>
-      <c r="C41" s="21" t="s">
-        <v>196</v>
-      </c>
       <c r="D41" s="22">
-        <v>0.007890312450832694</v>
+        <v>0.007870571999402243</v>
       </c>
     </row>
     <row r="42" spans="2:4">
       <c r="B42" s="20" t="s">
+        <v>196</v>
+      </c>
+      <c r="C42" s="21" t="s">
         <v>197</v>
-      </c>
-      <c r="C42" s="21" t="s">
-        <v>198</v>
       </c>
       <c r="D42" s="22">
         <v>0.006238200642540101</v>
@@ -2569,10 +2566,10 @@
     </row>
     <row r="43" spans="2:4">
       <c r="B43" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="C43" s="21" t="s">
         <v>199</v>
-      </c>
-      <c r="C43" s="21" t="s">
-        <v>200</v>
       </c>
       <c r="D43" s="22">
         <v>0.003131774061688995</v>
@@ -2580,21 +2577,21 @@
     </row>
     <row r="44" spans="2:4">
       <c r="B44" s="20" t="s">
+        <v>200</v>
+      </c>
+      <c r="C44" s="21" t="s">
         <v>201</v>
       </c>
-      <c r="C44" s="21" t="s">
-        <v>202</v>
-      </c>
       <c r="D44" s="22">
-        <v>0.001099359346361483</v>
+        <v>0.001059252672933397</v>
       </c>
     </row>
     <row r="45" spans="2:4">
       <c r="B45" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="C45" s="21" t="s">
         <v>203</v>
-      </c>
-      <c r="C45" s="21" t="s">
-        <v>204</v>
       </c>
       <c r="D45" s="22">
         <v>0.0003823096161312142</v>
@@ -2602,13 +2599,13 @@
     </row>
     <row r="46" spans="2:4">
       <c r="B46" s="20" t="s">
+        <v>204</v>
+      </c>
+      <c r="C46" s="20" t="s">
         <v>205</v>
       </c>
-      <c r="C46" s="20" t="s">
+      <c r="D46" s="20" t="s">
         <v>206</v>
-      </c>
-      <c r="D46" s="20" t="s">
-        <v>207</v>
       </c>
     </row>
   </sheetData>
@@ -2987,331 +2984,331 @@
     <row r="9" spans="1:22">
       <c r="A9" s="1"/>
       <c r="B9" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D9" s="10">
-        <v>0.175705869596844</v>
+        <v>0.1116997372977478</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G9" s="12">
-        <v>0.1375707572934353</v>
+        <v>0.1288846436469246</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J9" s="14">
-        <v>0.1185904442430068</v>
+        <v>0.1192441987548057</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="M9" s="16">
-        <v>0.1226124290290913</v>
+        <v>0.1233721263201689</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="P9" s="18">
-        <v>0.1181702038069988</v>
+        <v>0.118224665865319</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="S9" s="16">
-        <v>0.1176596434454658</v>
+        <v>0.1181337265409903</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="V9" s="18">
-        <v>0.161333233816655</v>
+        <v>0.1614954113906516</v>
       </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1"/>
       <c r="B10" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D10" s="10">
-        <v>0.09803724567291114</v>
+        <v>0.1083309866414919</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G10" s="12">
-        <v>0.1056482812164987</v>
+        <v>0.1222743984537696</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="J10" s="14">
-        <v>0.1165523620494276</v>
+        <v>0.1073039856073027</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="M10" s="16">
-        <v>0.1106162662025336</v>
+        <v>0.1118172250549103</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="O10" s="17" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="P10" s="18">
-        <v>0.1030920696728214</v>
+        <v>0.1021700899300668</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="S10" s="16">
-        <v>0.1093373536085624</v>
+        <v>0.1097643751402972</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="V10" s="18">
-        <v>0.116254872273746</v>
+        <v>0.1165190026019317</v>
       </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1"/>
       <c r="B11" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D11" s="10">
-        <v>0.05403399226959388</v>
+        <v>0.09493410353411502</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G11" s="12">
-        <v>0.09156616792401763</v>
+        <v>0.06882617809516436</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="J11" s="14">
-        <v>0.1055184424761909</v>
+        <v>0.1021821178325081</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="M11" s="16">
-        <v>0.09080210745365432</v>
+        <v>0.09134436808767422</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="O11" s="17" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="P11" s="18">
-        <v>0.09455432382052045</v>
+        <v>0.09591940826610984</v>
       </c>
       <c r="Q11" s="15" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="R11" s="15" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="S11" s="16">
-        <v>0.08729574399980537</v>
+        <v>0.08487487987583425</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="V11" s="18">
-        <v>0.1071653088315208</v>
+        <v>0.1077137362110677</v>
       </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1"/>
       <c r="B12" s="9" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D12" s="10">
-        <v>0.03082236784082055</v>
+        <v>0.09107597115364213</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G12" s="12">
-        <v>0.08912895199680977</v>
+        <v>0.03921978625232751</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="J12" s="14">
-        <v>0.100878041167142</v>
+        <v>0.1005272909580538</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="M12" s="16">
-        <v>0.08138240758888948</v>
+        <v>0.07608981509626707</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="O12" s="17" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="P12" s="18">
-        <v>0.0838271897763158</v>
+        <v>0.08361052048740517</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="S12" s="16">
-        <v>0.05762822810460065</v>
+        <v>0.05748302476034586</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="V12" s="18">
-        <v>0.05961021734906444</v>
+        <v>0.06103332788165901</v>
       </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1"/>
       <c r="B13" s="9" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D13" s="10">
-        <v>0.02205475480061745</v>
+        <v>0.05005213839451795</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G13" s="12">
-        <v>0.04878230568241439</v>
+        <v>0.02818656703931308</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="J13" s="14">
-        <v>0.03169384729086707</v>
+        <v>0.03247787150054663</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="M13" s="16">
-        <v>0.03738176818636919</v>
+        <v>0.03761451196135199</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="P13" s="18">
-        <v>0.02713494908647149</v>
+        <v>0.0279422537752531</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="S13" s="16">
-        <v>0.03060274271894342</v>
+        <v>0.03073338825845279</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="V13" s="18">
-        <v>0.02297629546341521</v>
+        <v>0.02304449024935901</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -3322,7 +3319,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -3331,7 +3328,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>53</v>
@@ -3340,7 +3337,7 @@
         <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>53</v>
@@ -3349,7 +3346,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>53</v>
@@ -3358,7 +3355,7 @@
         <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>53</v>
@@ -3367,7 +3364,7 @@
         <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>53</v>
@@ -3376,7 +3373,7 @@
         <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>53</v>
@@ -3385,331 +3382,331 @@
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D16" s="10">
-        <v>0.3514549579439779</v>
+        <v>0.1510158345720245</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G16" s="12">
-        <v>0.1469250432398405</v>
+        <v>0.2716350429372685</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="J16" s="14">
-        <v>0.1150947000783967</v>
+        <v>0.1196502085127667</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="M16" s="16">
-        <v>0.1439454179949652</v>
+        <v>0.1448951907887112</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="O16" s="17" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P16" s="18">
-        <v>0.1438079065584393</v>
+        <v>0.1428876021547997</v>
       </c>
       <c r="Q16" s="15" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="R16" s="15" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="S16" s="16">
-        <v>0.1427788164214941</v>
+        <v>0.1435818261083834</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="V16" s="18">
-        <v>0.13377170677417</v>
+        <v>0.1309253256188666</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D17" s="10">
-        <v>0.1165297840640698</v>
+        <v>0.09079179378939432</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G17" s="12">
-        <v>0.08829160293354099</v>
+        <v>0.1488479967000279</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J17" s="14">
-        <v>0.1060684869167681</v>
+        <v>0.1079178235234875</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="M17" s="16">
-        <v>0.1115087213703678</v>
+        <v>0.1122925474460847</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="O17" s="17" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="P17" s="18">
-        <v>0.09833555053079225</v>
+        <v>0.09783116224491321</v>
       </c>
       <c r="Q17" s="15" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="R17" s="15" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="S17" s="16">
-        <v>0.1257430589251604</v>
+        <v>0.126154050334251</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="V17" s="18">
-        <v>0.1208277545755314</v>
+        <v>0.1211059754685054</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D18" s="10">
-        <v>0.04573119069147102</v>
+        <v>0.06995982879902087</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G18" s="12">
-        <v>0.06726364401367846</v>
+        <v>0.05834642817073224</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="J18" s="14">
-        <v>0.07635568296189794</v>
+        <v>0.0770766569911529</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M18" s="16">
-        <v>0.07406155256979732</v>
+        <v>0.07436324047011331</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="O18" s="17" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="P18" s="18">
-        <v>0.08750938413029884</v>
+        <v>0.08831940299226526</v>
       </c>
       <c r="Q18" s="15" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="R18" s="15" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="S18" s="16">
-        <v>0.111917019833417</v>
+        <v>0.1111690726836092</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="V18" s="18">
-        <v>0.105933142916283</v>
+        <v>0.1059427492291615</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D19" s="10">
-        <v>0.03526414806197046</v>
+        <v>0.06817847815757705</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G19" s="12">
-        <v>0.06523154202431652</v>
+        <v>0.04428476708980128</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="J19" s="14">
-        <v>0.0491571007659596</v>
+        <v>0.05089691057831477</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="M19" s="16">
-        <v>0.04080439645673176</v>
+        <v>0.04100539345375705</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="O19" s="17" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P19" s="18">
-        <v>0.05275357389350857</v>
+        <v>0.05273700025472892</v>
       </c>
       <c r="Q19" s="15" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="R19" s="15" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="S19" s="16">
-        <v>0.06072866708263665</v>
+        <v>0.06098991053060364</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="U19" s="17" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="V19" s="18">
-        <v>0.05325647122366721</v>
+        <v>0.05351286926393127</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D20" s="10">
-        <v>0.0182261304243863</v>
+        <v>0.04073983724442813</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G20" s="12">
-        <v>0.03902432713618903</v>
+        <v>0.02316719099106261</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="J20" s="14">
-        <v>0.02907959793843693</v>
+        <v>0.02960282546445099</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="M20" s="16">
-        <v>0.03694551566330938</v>
+        <v>0.03648736553607387</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P20" s="18">
-        <v>0.05061635377314124</v>
+        <v>0.05016636220020698</v>
       </c>
       <c r="Q20" s="15" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="R20" s="15" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="S20" s="16">
-        <v>0.02274422030567649</v>
+        <v>0.02302258831736056</v>
       </c>
       <c r="T20" s="17" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="U20" s="17" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="V20" s="18">
-        <v>0.0302909098322644</v>
+        <v>0.02987141916889354</v>
       </c>
     </row>
   </sheetData>
